--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_zinc/harmonized.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_zinc/harmonized.xlsx
@@ -431,8 +431,8 @@
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
@@ -710,12 +710,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4:20-29</t>
+          <t>Hu:4:20-29</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4:10-20</t>
+          <t>Hu:4:10-20</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4:0-10</t>
+          <t>Hu:4:0-10</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4:-10-0</t>
+          <t>Ho:4:-10-0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -918,12 +918,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>4:-20--10</t>
+          <t>Ho:4:-20--10</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -970,12 +970,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4:-30--20</t>
+          <t>Ho:4:-30--20</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1005,7 +1005,7 @@
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4:-40--30</t>
+          <t>Ho:4:-40--30</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1057,7 +1057,7 @@
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4:-50--40</t>
+          <t>Ho:4:-50--40</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>4:-60--50</t>
+          <t>Ho:4:-60--50</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4:-70--60</t>
+          <t>Ho:4:-70--60</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1213,7 +1213,7 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1230,12 +1230,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4:-80--70</t>
+          <t>Ho:4:-80--70</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1265,7 +1265,7 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4:-90--80</t>
+          <t>Ho:4:-90--80</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1317,7 +1317,7 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1334,12 +1334,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4:-100--90</t>
+          <t>Ho:4:-100--90</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4:-125--100</t>
+          <t>Ho:4:-125--100</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1438,12 +1438,12 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>4:-150--125</t>
+          <t>Ho:4:-150--125</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1490,12 +1490,12 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4:-175--150</t>
+          <t>Ho:4:-175--150</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1542,12 +1542,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4:-200--175</t>
+          <t>Ho:4:-200--175</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>4:-250--200</t>
+          <t>Ho:4:-250--200</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1629,7 +1629,7 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>5:0-24</t>
+          <t>Hu:5:0-24</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5:10-18</t>
+          <t>Hu:5:10-18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1733,7 +1733,7 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5:0-10</t>
+          <t>Hu:5:0-10</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>5:-10-0</t>
+          <t>Ho:5:-10-0</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>5:-20--10</t>
+          <t>Ho:5:-20--10</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5:-30--20</t>
+          <t>Ho:5:-30--20</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -1958,12 +1958,12 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>5:-40--30</t>
+          <t>Ho:5:-40--30</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5:-50--40</t>
+          <t>Ho:5:-50--40</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2045,7 +2045,7 @@
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>5:-60--50</t>
+          <t>Ho:5:-60--50</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2114,12 +2114,12 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>5:-70--60</t>
+          <t>Ho:5:-70--60</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>5:-80--70</t>
+          <t>Ho:5:-80--70</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -2201,7 +2201,7 @@
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>5:-90--80</t>
+          <t>Ho:5:-90--80</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2270,12 +2270,12 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>5:-100--90</t>
+          <t>Ho:5:-100--90</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2305,7 +2305,7 @@
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>5:-125--100</t>
+          <t>Ho:5:-125--100</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
@@ -2357,7 +2357,7 @@
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2374,12 +2374,12 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>5:-150--125</t>
+          <t>Ho:5:-150--125</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2409,7 +2409,7 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2426,12 +2426,12 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>5:-175--150</t>
+          <t>Ho:5:-175--150</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>5:-200--175</t>
+          <t>Ho:5:-200--175</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -2513,7 +2513,7 @@
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2530,12 +2530,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>5:-250--200</t>
+          <t>Ho:5:-250--200</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -2565,7 +2565,7 @@
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2582,12 +2582,12 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>5:-300--250</t>
+          <t>Ho:5:-300--250</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2634,12 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>6:20-30</t>
+          <t>Hu:6:20-30</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2669,7 +2669,7 @@
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2686,12 +2686,12 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
@@ -2721,7 +2721,7 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2738,12 +2738,12 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -2773,7 +2773,7 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>6:10-20</t>
+          <t>Hu:6:10-20</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -2825,7 +2825,7 @@
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2842,12 +2842,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>6:0-10</t>
+          <t>Hu:6:0-10</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>6:-10-0</t>
+          <t>Ho:6:-10-0</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>6:-20--10</t>
+          <t>Ho:6:-20--10</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>6:-30--20</t>
+          <t>Ho:6:-30--20</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3033,7 +3033,7 @@
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>6:-40--30</t>
+          <t>Ho:6:-40--30</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -3085,7 +3085,7 @@
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3102,12 +3102,12 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>6:-50--40</t>
+          <t>Ho:6:-50--40</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3154,12 +3154,12 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>6:-60--50</t>
+          <t>Ho:6:-60--50</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3206,12 +3206,12 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>6:-70--60</t>
+          <t>Ho:6:-70--60</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3258,12 +3258,12 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>6:-80--70</t>
+          <t>Ho:6:-80--70</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
@@ -3293,7 +3293,7 @@
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>6:-90--80</t>
+          <t>Ho:6:-90--80</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3362,12 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>6:-100--90</t>
+          <t>Ho:6:-100--90</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
@@ -3397,7 +3397,7 @@
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3414,12 +3414,12 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>6:-125--100</t>
+          <t>Ho:6:-125--100</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>6:-150--125</t>
+          <t>Ho:6:-150--125</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -3501,7 +3501,7 @@
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>6:-175--150</t>
+          <t>Ho:6:-175--150</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -3553,7 +3553,7 @@
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>6:-200--175</t>
+          <t>Ho:6:-200--175</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3622,12 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>6:-250--200</t>
+          <t>Ho:6:-250--200</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3657,7 +3657,7 @@
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3674,12 +3674,12 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3726,12 +3726,12 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>7:20-22</t>
+          <t>Hu:7:20-22</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
@@ -3761,7 +3761,7 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3778,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>7:10-20</t>
+          <t>Hu:7:10-20</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -3813,7 +3813,7 @@
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3830,12 +3830,12 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>7:0-10</t>
+          <t>Hu:7:0-10</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
@@ -3865,7 +3865,7 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3882,12 +3882,12 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>7:-10-0</t>
+          <t>Ho:7:-10-0</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>7:-20--10</t>
+          <t>Ho:7:-20--10</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -3986,12 +3986,12 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>7:-30--20</t>
+          <t>Ho:7:-30--20</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4038,12 +4038,12 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>7:-40--30</t>
+          <t>Ho:7:-40--30</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4073,7 +4073,7 @@
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4090,12 +4090,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>7:-50--40</t>
+          <t>Ho:7:-50--40</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -4125,7 +4125,7 @@
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>7:-60--50</t>
+          <t>Ho:7:-60--50</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4177,7 +4177,7 @@
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4194,12 +4194,12 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>7:-70--60</t>
+          <t>Ho:7:-70--60</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
@@ -4229,7 +4229,7 @@
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4246,12 +4246,12 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>7:-80--70</t>
+          <t>Ho:7:-80--70</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>7:-90--80</t>
+          <t>Ho:7:-90--80</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
@@ -4333,7 +4333,7 @@
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>7:-100--90</t>
+          <t>Ho:7:-100--90</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
@@ -4385,7 +4385,7 @@
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4402,12 +4402,12 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>7:-125--100</t>
+          <t>Ho:7:-125--100</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -4437,7 +4437,7 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4454,12 +4454,12 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>7:-150--125</t>
+          <t>Ho:7:-150--125</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>7:-175--150</t>
+          <t>Ho:7:-175--150</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
@@ -4541,7 +4541,7 @@
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4558,12 +4558,12 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>7:-200--175</t>
+          <t>Ho:7:-200--175</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
@@ -4593,7 +4593,7 @@
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4610,12 +4610,12 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>7:-250--200</t>
+          <t>Ho:7:-250--200</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4662,12 +4662,12 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>7:-300--250</t>
+          <t>Ho:7:-300--250</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4714,12 +4714,12 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>8:10-20</t>
+          <t>Hu:8:10-20</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E83" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4766,12 +4766,12 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>8:0-10</t>
+          <t>Hu:8:0-10</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E84" s="2" t="inlineStr">
@@ -4801,7 +4801,7 @@
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4818,12 +4818,12 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Hu:8:-10-0</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4870,12 +4870,12 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>8:-10-0</t>
+          <t>Ho:8:-10-0</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4922,12 +4922,12 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>8:-20--10</t>
+          <t>Ho:8:-20--10</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
@@ -4957,7 +4957,7 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -4974,12 +4974,12 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>8:-30--20</t>
+          <t>Ho:8:-30--20</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5009,7 +5009,7 @@
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5026,12 +5026,12 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>8:-40--30</t>
+          <t>Ho:8:-40--30</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E89" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5078,12 +5078,12 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>8:-50--40</t>
+          <t>Ho:8:-50--40</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
@@ -5113,7 +5113,7 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>8:-60--50</t>
+          <t>Ho:8:-60--50</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>8:-70--60</t>
+          <t>Ho:8:-70--60</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5234,12 +5234,12 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>8:-80--70</t>
+          <t>Ho:8:-80--70</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
@@ -5269,7 +5269,7 @@
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>8:-90--80</t>
+          <t>Ho:8:-90--80</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
@@ -5321,7 +5321,7 @@
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5338,12 +5338,12 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>8:-100--90</t>
+          <t>Ho:8:-100--90</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E95" s="2" t="inlineStr">
@@ -5373,7 +5373,7 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5390,12 +5390,12 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>8:-125--100</t>
+          <t>Ho:8:-125--100</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5442,12 +5442,12 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>8:-150--125</t>
+          <t>Ho:8:-150--125</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5494,12 +5494,12 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>8:-175--150</t>
+          <t>Ho:8:-175--150</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -5529,7 +5529,7 @@
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>8:-200--175</t>
+          <t>Ho:8:-200--175</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5598,12 +5598,12 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>9:10-18</t>
+          <t>Hu:9:10-18</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -5633,7 +5633,7 @@
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5650,12 +5650,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>9:0-10</t>
+          <t>Hu:9:0-10</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -5685,7 +5685,7 @@
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5702,12 +5702,12 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>9:-10-0</t>
+          <t>Ho:9:-10-0</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5737,7 +5737,7 @@
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>9:-20--10</t>
+          <t>Ho:9:-20--10</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5806,12 +5806,12 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>9:-30--20</t>
+          <t>Ho:9:-30--20</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5841,7 +5841,7 @@
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5858,12 +5858,12 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>9:-40--30</t>
+          <t>Ho:9:-40--30</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -5893,7 +5893,7 @@
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5910,12 +5910,12 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>9:-50--40</t>
+          <t>Ho:9:-50--40</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5945,7 +5945,7 @@
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -5962,12 +5962,12 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>9:-60--50</t>
+          <t>Ho:9:-60--50</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5997,7 +5997,7 @@
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6014,12 +6014,12 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>9:-70--60</t>
+          <t>Ho:9:-70--60</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6066,12 +6066,12 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>9:-80--70</t>
+          <t>Ho:9:-80--70</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6118,12 +6118,12 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>9:-90--80</t>
+          <t>Ho:9:-90--80</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
@@ -6153,7 +6153,7 @@
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>9:-100--90</t>
+          <t>Ho:9:-100--90</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
@@ -6205,7 +6205,7 @@
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6222,12 +6222,12 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>9:-125--100</t>
+          <t>Ho:9:-125--100</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -6257,7 +6257,7 @@
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6274,12 +6274,12 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>9:-150--125</t>
+          <t>Ho:9:-150--125</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -6309,7 +6309,7 @@
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>9:-175--150</t>
+          <t>Ho:9:-175--150</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E114" s="2" t="inlineStr">
@@ -6361,7 +6361,7 @@
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6378,12 +6378,12 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>9:-200--175</t>
+          <t>Ho:9:-200--175</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -6413,7 +6413,7 @@
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6430,12 +6430,12 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>9:-250--200</t>
+          <t>Ho:9:-250--200</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -6465,7 +6465,7 @@
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6482,12 +6482,12 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>9:-300--250</t>
+          <t>Ho:9:-300--250</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -6517,7 +6517,7 @@
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>10:20-29</t>
+          <t>Hu:10:20-29</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E118" s="2" t="inlineStr">
@@ -6569,7 +6569,7 @@
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6586,12 +6586,12 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>10:10-20</t>
+          <t>Hu:10:10-20</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
@@ -6621,7 +6621,7 @@
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6638,12 +6638,12 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>10:0-10</t>
+          <t>Hu:10:0-10</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
@@ -6673,7 +6673,7 @@
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>10:-10-0</t>
+          <t>Ho:10:-10-0</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E121" s="2" t="inlineStr">
@@ -6725,7 +6725,7 @@
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6742,12 +6742,12 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>10:-20--10</t>
+          <t>Ho:10:-20--10</t>
         </is>
       </c>
       <c r="D122" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E122" s="2" t="inlineStr">
@@ -6777,7 +6777,7 @@
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6794,12 +6794,12 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>10:-30--20</t>
+          <t>Ho:10:-30--20</t>
         </is>
       </c>
       <c r="D123" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E123" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6846,12 +6846,12 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>10:-40--30</t>
+          <t>Ho:10:-40--30</t>
         </is>
       </c>
       <c r="D124" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E124" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>10:-50--40</t>
+          <t>Ho:10:-50--40</t>
         </is>
       </c>
       <c r="D125" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E125" s="2" t="inlineStr">
@@ -6933,7 +6933,7 @@
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -6950,12 +6950,12 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>10:-60--50</t>
+          <t>Ho:10:-60--50</t>
         </is>
       </c>
       <c r="D126" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E126" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7002,12 +7002,12 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>10:-70--60</t>
+          <t>Ho:10:-70--60</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -7037,7 +7037,7 @@
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7054,12 +7054,12 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>10:-80--70</t>
+          <t>Ho:10:-80--70</t>
         </is>
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7106,12 +7106,12 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>10:-90--80</t>
+          <t>Ho:10:-90--80</t>
         </is>
       </c>
       <c r="D129" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E129" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7158,12 +7158,12 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>10:-100--90</t>
+          <t>Ho:10:-100--90</t>
         </is>
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E130" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7210,12 +7210,12 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>10:-125--100</t>
+          <t>Ho:10:-125--100</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E131" s="2" t="inlineStr">
@@ -7245,7 +7245,7 @@
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7262,12 +7262,12 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>10:-150--125</t>
+          <t>Ho:10:-150--125</t>
         </is>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E132" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7314,12 +7314,12 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>10:-175--150</t>
+          <t>Ho:10:-175--150</t>
         </is>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7366,12 +7366,12 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>10:-200--175</t>
+          <t>Ho:10:-200--175</t>
         </is>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E134" s="2" t="inlineStr">
@@ -7401,7 +7401,7 @@
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7418,12 +7418,12 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>10:-225--200</t>
+          <t>Ho:10:-225--200</t>
         </is>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr">
@@ -7453,7 +7453,7 @@
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7470,12 +7470,12 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>10:-255--225</t>
+          <t>Ho:10:-255--225</t>
         </is>
       </c>
       <c r="D136" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E136" s="2" t="inlineStr">
@@ -7505,7 +7505,7 @@
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7522,12 +7522,12 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>10:-275--255</t>
+          <t>Ho:10:-275--255</t>
         </is>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
@@ -7557,7 +7557,7 @@
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7574,12 +7574,12 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>11:10-18</t>
+          <t>Hu:11:10-18</t>
         </is>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E138" s="2" t="inlineStr">
@@ -7609,7 +7609,7 @@
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7626,12 +7626,12 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>11:0-10</t>
+          <t>Hu:11:0-10</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E139" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7678,12 +7678,12 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>11:-10-0</t>
+          <t>Ho:11:-10-0</t>
         </is>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E140" s="2" t="inlineStr">
@@ -7713,7 +7713,7 @@
       <c r="K140" s="2" t="inlineStr"/>
       <c r="L140" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7730,12 +7730,12 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>11:-20--10</t>
+          <t>Ho:11:-20--10</t>
         </is>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E141" s="2" t="inlineStr">
@@ -7765,7 +7765,7 @@
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7782,12 +7782,12 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>11:-30--20</t>
+          <t>Ho:11:-30--20</t>
         </is>
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -7817,7 +7817,7 @@
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>11:-40--30</t>
+          <t>Ho:11:-40--30</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E143" s="2" t="inlineStr">
@@ -7869,7 +7869,7 @@
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7886,12 +7886,12 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>11:-50--40</t>
+          <t>Ho:11:-50--40</t>
         </is>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E144" s="2" t="inlineStr">
@@ -7921,7 +7921,7 @@
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7938,12 +7938,12 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>11:-60--50</t>
+          <t>Ho:11:-60--50</t>
         </is>
       </c>
       <c r="D145" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E145" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -7990,12 +7990,12 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>11:-70--60</t>
+          <t>Ho:11:-70--60</t>
         </is>
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E146" s="2" t="inlineStr">
@@ -8025,7 +8025,7 @@
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8042,12 +8042,12 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>11:-80--70</t>
+          <t>Ho:11:-80--70</t>
         </is>
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E147" s="2" t="inlineStr">
@@ -8077,7 +8077,7 @@
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8094,12 +8094,12 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>11:-90--80</t>
+          <t>Ho:11:-90--80</t>
         </is>
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -8129,7 +8129,7 @@
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8146,12 +8146,12 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>11:-100--90</t>
+          <t>Ho:11:-100--90</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E149" s="2" t="inlineStr">
@@ -8181,7 +8181,7 @@
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8198,12 +8198,12 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>11:-125--100</t>
+          <t>Ho:11:-125--100</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E150" s="2" t="inlineStr">
@@ -8233,7 +8233,7 @@
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8250,12 +8250,12 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>11:-150--125</t>
+          <t>Ho:11:-150--125</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E151" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8302,12 +8302,12 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>11:-175--150</t>
+          <t>Ho:11:-175--150</t>
         </is>
       </c>
       <c r="D152" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E152" s="2" t="inlineStr">
@@ -8337,7 +8337,7 @@
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>11:-200--175</t>
+          <t>Ho:11:-200--175</t>
         </is>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E153" s="2" t="inlineStr">
@@ -8389,7 +8389,7 @@
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>11:-250--200</t>
+          <t>Ho:11:-250--200</t>
         </is>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E154" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8458,12 +8458,12 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>13:20-25</t>
+          <t>Hu:13:20-25</t>
         </is>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E155" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8510,12 +8510,12 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>13:10-20</t>
+          <t>Hu:13:10-20</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E156" s="2" t="inlineStr">
@@ -8545,7 +8545,7 @@
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>13:0-10</t>
+          <t>Hu:13:0-10</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -8597,7 +8597,7 @@
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8614,12 +8614,12 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Hu:13:-10-0</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E158" s="2" t="inlineStr">
@@ -8649,7 +8649,7 @@
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8666,12 +8666,12 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>13:-10-0</t>
+          <t>Ho:13:-10-0</t>
         </is>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E159" s="2" t="inlineStr">
@@ -8701,7 +8701,7 @@
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8718,12 +8718,12 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>13:-20--10</t>
+          <t>Ho:13:-20--10</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E160" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       <c r="K160" s="2" t="inlineStr"/>
       <c r="L160" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8770,12 +8770,12 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>13:-30--20</t>
+          <t>Ho:13:-30--20</t>
         </is>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E161" s="2" t="inlineStr">
@@ -8805,7 +8805,7 @@
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8822,12 +8822,12 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>13:-40--30</t>
+          <t>Ho:13:-40--30</t>
         </is>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E162" s="2" t="inlineStr">
@@ -8857,7 +8857,7 @@
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8874,12 +8874,12 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>13:-50--40</t>
+          <t>Ho:13:-50--40</t>
         </is>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E163" s="2" t="inlineStr">
@@ -8909,7 +8909,7 @@
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8926,12 +8926,12 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>13:-60--50</t>
+          <t>Ho:13:-60--50</t>
         </is>
       </c>
       <c r="D164" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E164" s="2" t="inlineStr">
@@ -8961,7 +8961,7 @@
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -8978,12 +8978,12 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>13:-70--60</t>
+          <t>Ho:13:-70--60</t>
         </is>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E165" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9030,12 +9030,12 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>13:-80--70</t>
+          <t>Ho:13:-80--70</t>
         </is>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E166" s="2" t="inlineStr">
@@ -9065,7 +9065,7 @@
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9082,12 +9082,12 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>13:-90--80</t>
+          <t>Ho:13:-90--80</t>
         </is>
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E167" s="2" t="inlineStr">
@@ -9117,7 +9117,7 @@
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9134,12 +9134,12 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>13:-100--90</t>
+          <t>Ho:13:-100--90</t>
         </is>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E168" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9186,12 +9186,12 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>13:-125--100</t>
+          <t>Ho:13:-125--100</t>
         </is>
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E169" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9238,12 +9238,12 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>13:-150--125</t>
+          <t>Ho:13:-150--125</t>
         </is>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E170" s="2" t="inlineStr">
@@ -9273,7 +9273,7 @@
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9290,12 +9290,12 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>13:-175--150</t>
+          <t>Ho:13:-175--150</t>
         </is>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E171" s="2" t="inlineStr">
@@ -9325,7 +9325,7 @@
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9342,12 +9342,12 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>13:-200--175</t>
+          <t>Ho:13:-200--175</t>
         </is>
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E172" s="2" t="inlineStr">
@@ -9377,7 +9377,7 @@
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9394,12 +9394,12 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>13:-250--200</t>
+          <t>Ho:13:-250--200</t>
         </is>
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E173" s="2" t="inlineStr">
@@ -9429,7 +9429,7 @@
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9446,12 +9446,12 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>13:-270--250</t>
+          <t>Ho:13:-270--250</t>
         </is>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E174" s="2" t="inlineStr">
@@ -9481,7 +9481,7 @@
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>13:-300--270</t>
+          <t>Ho:13:-300--270</t>
         </is>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E175" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>14:0-10</t>
+          <t>Hu:14:0-10</t>
         </is>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E176" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9602,12 +9602,12 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>14:-10-0</t>
+          <t>Ho:14:-10-0</t>
         </is>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E177" s="2" t="inlineStr">
@@ -9637,7 +9637,7 @@
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9654,12 +9654,12 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>14:-20--10</t>
+          <t>Ho:14:-20--10</t>
         </is>
       </c>
       <c r="D178" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E178" s="2" t="inlineStr">
@@ -9689,7 +9689,7 @@
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9706,12 +9706,12 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>14:-30--20</t>
+          <t>Ho:14:-30--20</t>
         </is>
       </c>
       <c r="D179" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E179" s="2" t="inlineStr">
@@ -9741,7 +9741,7 @@
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9758,12 +9758,12 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>14:-40--30</t>
+          <t>Ho:14:-40--30</t>
         </is>
       </c>
       <c r="D180" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E180" s="2" t="inlineStr">
@@ -9793,7 +9793,7 @@
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9810,12 +9810,12 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>14:-50--40</t>
+          <t>Ho:14:-50--40</t>
         </is>
       </c>
       <c r="D181" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E181" s="2" t="inlineStr">
@@ -9845,7 +9845,7 @@
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9862,12 +9862,12 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>14:-60--50</t>
+          <t>Ho:14:-60--50</t>
         </is>
       </c>
       <c r="D182" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E182" s="2" t="inlineStr">
@@ -9897,7 +9897,7 @@
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>14:-70--60</t>
+          <t>Ho:14:-70--60</t>
         </is>
       </c>
       <c r="D183" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E183" s="2" t="inlineStr">
@@ -9949,7 +9949,7 @@
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -9966,12 +9966,12 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>14:-80--70</t>
+          <t>Ho:14:-80--70</t>
         </is>
       </c>
       <c r="D184" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E184" s="2" t="inlineStr">
@@ -10001,7 +10001,7 @@
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10018,12 +10018,12 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>14:-90--80</t>
+          <t>Ho:14:-90--80</t>
         </is>
       </c>
       <c r="D185" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E185" s="2" t="inlineStr">
@@ -10053,7 +10053,7 @@
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10070,12 +10070,12 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>14:-100--90</t>
+          <t>Ho:14:-100--90</t>
         </is>
       </c>
       <c r="D186" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E186" s="2" t="inlineStr">
@@ -10105,7 +10105,7 @@
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>14:-125--100</t>
+          <t>Ho:14:-125--100</t>
         </is>
       </c>
       <c r="D187" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E187" s="2" t="inlineStr">
@@ -10157,7 +10157,7 @@
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10174,12 +10174,12 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>14:-150--125</t>
+          <t>Ho:14:-150--125</t>
         </is>
       </c>
       <c r="D188" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E188" s="2" t="inlineStr">
@@ -10209,7 +10209,7 @@
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10226,12 +10226,12 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>14:-175--150</t>
+          <t>Ho:14:-175--150</t>
         </is>
       </c>
       <c r="D189" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E189" s="2" t="inlineStr">
@@ -10261,7 +10261,7 @@
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10278,12 +10278,12 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>14:-200--175</t>
+          <t>Ho:14:-200--175</t>
         </is>
       </c>
       <c r="D190" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E190" s="2" t="inlineStr">
@@ -10313,7 +10313,7 @@
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10330,12 +10330,12 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>14:-215--200</t>
+          <t>Ho:14:-215--200</t>
         </is>
       </c>
       <c r="D191" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E191" s="2" t="inlineStr">
@@ -10365,7 +10365,7 @@
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10382,12 +10382,12 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>14:-220--215</t>
+          <t>Ho:14:-220--215</t>
         </is>
       </c>
       <c r="D192" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E192" s="2" t="inlineStr">
@@ -10417,7 +10417,7 @@
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10434,12 +10434,12 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>15:20-24</t>
+          <t>Hu:15:20-24</t>
         </is>
       </c>
       <c r="D193" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E193" s="2" t="inlineStr">
@@ -10469,7 +10469,7 @@
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10486,12 +10486,12 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>15:10-20</t>
+          <t>Hu:15:10-20</t>
         </is>
       </c>
       <c r="D194" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E194" s="2" t="inlineStr">
@@ -10521,7 +10521,7 @@
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10538,12 +10538,12 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>15:0-10</t>
+          <t>Hu:15:0-10</t>
         </is>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E195" s="2" t="inlineStr">
@@ -10573,7 +10573,7 @@
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10590,12 +10590,12 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Hu:15:-10-0</t>
         </is>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E196" s="2" t="inlineStr">
@@ -10625,7 +10625,7 @@
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10642,12 +10642,12 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>15:-10-0</t>
+          <t>Ho:15:-10-0</t>
         </is>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E197" s="2" t="inlineStr">
@@ -10677,7 +10677,7 @@
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10694,12 +10694,12 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>15:-20--10</t>
+          <t>Ho:15:-20--10</t>
         </is>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E198" s="2" t="inlineStr">
@@ -10729,7 +10729,7 @@
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10746,12 +10746,12 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>15:-30--20</t>
+          <t>Ho:15:-30--20</t>
         </is>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
@@ -10781,7 +10781,7 @@
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10798,12 +10798,12 @@
       </c>
       <c r="C200" s="2" t="inlineStr">
         <is>
-          <t>15:-40--30</t>
+          <t>Ho:15:-40--30</t>
         </is>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E200" s="2" t="inlineStr">
@@ -10833,7 +10833,7 @@
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10850,12 +10850,12 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>15:-50--40</t>
+          <t>Ho:15:-50--40</t>
         </is>
       </c>
       <c r="D201" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E201" s="2" t="inlineStr">
@@ -10885,7 +10885,7 @@
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10902,12 +10902,12 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>15:-60--50</t>
+          <t>Ho:15:-60--50</t>
         </is>
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E202" s="2" t="inlineStr">
@@ -10937,7 +10937,7 @@
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -10954,12 +10954,12 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>15:-70--60</t>
+          <t>Ho:15:-70--60</t>
         </is>
       </c>
       <c r="D203" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E203" s="2" t="inlineStr">
@@ -10989,7 +10989,7 @@
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11006,12 +11006,12 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>15:-80--70</t>
+          <t>Ho:15:-80--70</t>
         </is>
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E204" s="2" t="inlineStr">
@@ -11041,7 +11041,7 @@
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11058,12 +11058,12 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>15:-90--80</t>
+          <t>Ho:15:-90--80</t>
         </is>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E205" s="2" t="inlineStr">
@@ -11093,7 +11093,7 @@
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11110,12 +11110,12 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>15:-100--90</t>
+          <t>Ho:15:-100--90</t>
         </is>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E206" s="2" t="inlineStr">
@@ -11145,7 +11145,7 @@
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11162,12 +11162,12 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>15:-125--100</t>
+          <t>Ho:15:-125--100</t>
         </is>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E207" s="2" t="inlineStr">
@@ -11197,7 +11197,7 @@
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11214,12 +11214,12 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>15:-150--125</t>
+          <t>Ho:15:-150--125</t>
         </is>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E208" s="2" t="inlineStr">
@@ -11249,7 +11249,7 @@
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11266,12 +11266,12 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>16:20-29</t>
+          <t>Hu:16:20-29</t>
         </is>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E209" s="2" t="inlineStr">
@@ -11301,7 +11301,7 @@
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11318,12 +11318,12 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>16:10-20</t>
+          <t>Hu:16:10-20</t>
         </is>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E210" s="2" t="inlineStr">
@@ -11353,7 +11353,7 @@
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11370,12 +11370,12 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>16:0-10</t>
+          <t>Hu:16:0-10</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
@@ -11405,7 +11405,7 @@
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11422,12 +11422,12 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Hu:16:-10-0</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
@@ -11457,7 +11457,7 @@
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11474,12 +11474,12 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>16:-10-0</t>
+          <t>Ho:16:-10-0</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11526,12 +11526,12 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>16:-20--10</t>
+          <t>Ho:16:-20--10</t>
         </is>
       </c>
       <c r="D214" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E214" s="2" t="inlineStr">
@@ -11561,7 +11561,7 @@
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11578,12 +11578,12 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>16:-30--20</t>
+          <t>Ho:16:-30--20</t>
         </is>
       </c>
       <c r="D215" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E215" s="2" t="inlineStr">
@@ -11613,7 +11613,7 @@
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11630,12 +11630,12 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>16:-40--30</t>
+          <t>Ho:16:-40--30</t>
         </is>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E216" s="2" t="inlineStr">
@@ -11665,7 +11665,7 @@
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11682,12 +11682,12 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>16:-50--40</t>
+          <t>Ho:16:-50--40</t>
         </is>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E217" s="2" t="inlineStr">
@@ -11717,7 +11717,7 @@
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11734,12 +11734,12 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>16:-60--50</t>
+          <t>Ho:16:-60--50</t>
         </is>
       </c>
       <c r="D218" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E218" s="2" t="inlineStr">
@@ -11769,7 +11769,7 @@
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11786,12 +11786,12 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>16:-70--60</t>
+          <t>Ho:16:-70--60</t>
         </is>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E219" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11838,12 +11838,12 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>16:-80--70</t>
+          <t>Ho:16:-80--70</t>
         </is>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E220" s="2" t="inlineStr">
@@ -11873,7 +11873,7 @@
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11890,12 +11890,12 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>16:-90--80</t>
+          <t>Ho:16:-90--80</t>
         </is>
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E221" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11942,12 +11942,12 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>16:-100--90</t>
+          <t>Ho:16:-100--90</t>
         </is>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E222" s="2" t="inlineStr">
@@ -11977,7 +11977,7 @@
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -11994,12 +11994,12 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>16:-125--100</t>
+          <t>Ho:16:-125--100</t>
         </is>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E223" s="2" t="inlineStr">
@@ -12029,7 +12029,7 @@
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12046,12 +12046,12 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>16:-150--125</t>
+          <t>Ho:16:-150--125</t>
         </is>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E224" s="2" t="inlineStr">
@@ -12081,7 +12081,7 @@
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12098,12 +12098,12 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>16:-175--150</t>
+          <t>Ho:16:-175--150</t>
         </is>
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E225" s="2" t="inlineStr">
@@ -12133,7 +12133,7 @@
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12150,12 +12150,12 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>16:-200--175</t>
+          <t>Ho:16:-200--175</t>
         </is>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E226" s="2" t="inlineStr">
@@ -12185,7 +12185,7 @@
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12202,12 +12202,12 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>16:-250--200</t>
+          <t>Ho:16:-250--200</t>
         </is>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E227" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12254,12 +12254,12 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>17:20-25</t>
+          <t>Hu:17:20-25</t>
         </is>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E228" s="2" t="inlineStr">
@@ -12289,7 +12289,7 @@
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12306,12 +12306,12 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>17:10-20</t>
+          <t>Hu:17:10-20</t>
         </is>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E229" s="2" t="inlineStr">
@@ -12341,7 +12341,7 @@
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12358,12 +12358,12 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>17:0-10</t>
+          <t>Hu:17:0-10</t>
         </is>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E230" s="2" t="inlineStr">
@@ -12393,7 +12393,7 @@
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12410,12 +12410,12 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Hu:17:-10-0</t>
         </is>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E231" s="2" t="inlineStr">
@@ -12445,7 +12445,7 @@
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12462,12 +12462,12 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>17:-10-0</t>
+          <t>Ho:17:-10-0</t>
         </is>
       </c>
       <c r="D232" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E232" s="2" t="inlineStr">
@@ -12497,7 +12497,7 @@
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12514,12 +12514,12 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>17:-20--10</t>
+          <t>Ho:17:-20--10</t>
         </is>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E233" s="2" t="inlineStr">
@@ -12549,7 +12549,7 @@
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12566,12 +12566,12 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>17:-30--20</t>
+          <t>Ho:17:-30--20</t>
         </is>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E234" s="2" t="inlineStr">
@@ -12601,7 +12601,7 @@
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12618,12 +12618,12 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>17:-40--30</t>
+          <t>Ho:17:-40--30</t>
         </is>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E235" s="2" t="inlineStr">
@@ -12653,7 +12653,7 @@
       <c r="K235" s="2" t="inlineStr"/>
       <c r="L235" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12670,12 +12670,12 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>17:-50--40</t>
+          <t>Ho:17:-50--40</t>
         </is>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E236" s="2" t="inlineStr">
@@ -12705,7 +12705,7 @@
       <c r="K236" s="2" t="inlineStr"/>
       <c r="L236" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12722,12 +12722,12 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>17:-60--50</t>
+          <t>Ho:17:-60--50</t>
         </is>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E237" s="2" t="inlineStr">
@@ -12757,7 +12757,7 @@
       <c r="K237" s="2" t="inlineStr"/>
       <c r="L237" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12774,12 +12774,12 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>17:-70--60</t>
+          <t>Ho:17:-70--60</t>
         </is>
       </c>
       <c r="D238" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E238" s="2" t="inlineStr">
@@ -12809,7 +12809,7 @@
       <c r="K238" s="2" t="inlineStr"/>
       <c r="L238" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12826,12 +12826,12 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>17:-80--70</t>
+          <t>Ho:17:-80--70</t>
         </is>
       </c>
       <c r="D239" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E239" s="2" t="inlineStr">
@@ -12861,7 +12861,7 @@
       <c r="K239" s="2" t="inlineStr"/>
       <c r="L239" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12878,12 +12878,12 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>17:-90--80</t>
+          <t>Ho:17:-90--80</t>
         </is>
       </c>
       <c r="D240" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E240" s="2" t="inlineStr">
@@ -12913,7 +12913,7 @@
       <c r="K240" s="2" t="inlineStr"/>
       <c r="L240" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12930,12 +12930,12 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>17:-100--90</t>
+          <t>Ho:17:-100--90</t>
         </is>
       </c>
       <c r="D241" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E241" s="2" t="inlineStr">
@@ -12965,7 +12965,7 @@
       <c r="K241" s="2" t="inlineStr"/>
       <c r="L241" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -12982,12 +12982,12 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>17:-125--100</t>
+          <t>Ho:17:-125--100</t>
         </is>
       </c>
       <c r="D242" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E242" s="2" t="inlineStr">
@@ -13017,7 +13017,7 @@
       <c r="K242" s="2" t="inlineStr"/>
       <c r="L242" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13034,12 +13034,12 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>17:-150--125</t>
+          <t>Ho:17:-150--125</t>
         </is>
       </c>
       <c r="D243" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E243" s="2" t="inlineStr">
@@ -13069,7 +13069,7 @@
       <c r="K243" s="2" t="inlineStr"/>
       <c r="L243" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13086,12 +13086,12 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>17:-175--150</t>
+          <t>Ho:17:-175--150</t>
         </is>
       </c>
       <c r="D244" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E244" s="2" t="inlineStr">
@@ -13121,7 +13121,7 @@
       <c r="K244" s="2" t="inlineStr"/>
       <c r="L244" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13138,12 +13138,12 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>17:-200--175</t>
+          <t>Ho:17:-200--175</t>
         </is>
       </c>
       <c r="D245" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E245" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       <c r="K245" s="2" t="inlineStr"/>
       <c r="L245" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13190,12 +13190,12 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>17:-239--200</t>
+          <t>Ho:17:-239--200</t>
         </is>
       </c>
       <c r="D246" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E246" s="2" t="inlineStr">
@@ -13225,7 +13225,7 @@
       <c r="K246" s="2" t="inlineStr"/>
       <c r="L246" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13242,12 +13242,12 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>19:10-20</t>
+          <t>Hu:19:10-20</t>
         </is>
       </c>
       <c r="D247" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E247" s="2" t="inlineStr">
@@ -13277,7 +13277,7 @@
       <c r="K247" s="2" t="inlineStr"/>
       <c r="L247" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13294,12 +13294,12 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>19:0-10</t>
+          <t>Hu:19:0-10</t>
         </is>
       </c>
       <c r="D248" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E248" s="2" t="inlineStr">
@@ -13329,7 +13329,7 @@
       <c r="K248" s="2" t="inlineStr"/>
       <c r="L248" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13346,12 +13346,12 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>19:-10-0</t>
+          <t>Ho:19:-10-0</t>
         </is>
       </c>
       <c r="D249" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E249" s="2" t="inlineStr">
@@ -13381,7 +13381,7 @@
       <c r="K249" s="2" t="inlineStr"/>
       <c r="L249" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13398,12 +13398,12 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>19:-20--10</t>
+          <t>Ho:19:-20--10</t>
         </is>
       </c>
       <c r="D250" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E250" s="2" t="inlineStr">
@@ -13433,7 +13433,7 @@
       <c r="K250" s="2" t="inlineStr"/>
       <c r="L250" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13450,12 +13450,12 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>19:-30--20</t>
+          <t>Ho:19:-30--20</t>
         </is>
       </c>
       <c r="D251" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E251" s="2" t="inlineStr">
@@ -13485,7 +13485,7 @@
       <c r="K251" s="2" t="inlineStr"/>
       <c r="L251" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13502,12 +13502,12 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>19:-40--30</t>
+          <t>Ho:19:-40--30</t>
         </is>
       </c>
       <c r="D252" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E252" s="2" t="inlineStr">
@@ -13537,7 +13537,7 @@
       <c r="K252" s="2" t="inlineStr"/>
       <c r="L252" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13554,12 +13554,12 @@
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>19:-50--40</t>
+          <t>Ho:19:-50--40</t>
         </is>
       </c>
       <c r="D253" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E253" s="2" t="inlineStr">
@@ -13589,7 +13589,7 @@
       <c r="K253" s="2" t="inlineStr"/>
       <c r="L253" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13606,12 +13606,12 @@
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>19:-60--50</t>
+          <t>Ho:19:-60--50</t>
         </is>
       </c>
       <c r="D254" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E254" s="2" t="inlineStr">
@@ -13641,7 +13641,7 @@
       <c r="K254" s="2" t="inlineStr"/>
       <c r="L254" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13658,12 +13658,12 @@
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>19:-70--60</t>
+          <t>Ho:19:-70--60</t>
         </is>
       </c>
       <c r="D255" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E255" s="2" t="inlineStr">
@@ -13693,7 +13693,7 @@
       <c r="K255" s="2" t="inlineStr"/>
       <c r="L255" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13710,12 +13710,12 @@
       </c>
       <c r="C256" s="2" t="inlineStr">
         <is>
-          <t>19:-80--70</t>
+          <t>Ho:19:-80--70</t>
         </is>
       </c>
       <c r="D256" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E256" s="2" t="inlineStr">
@@ -13745,7 +13745,7 @@
       <c r="K256" s="2" t="inlineStr"/>
       <c r="L256" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13762,12 +13762,12 @@
       </c>
       <c r="C257" s="2" t="inlineStr">
         <is>
-          <t>19:-90--80</t>
+          <t>Ho:19:-90--80</t>
         </is>
       </c>
       <c r="D257" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E257" s="2" t="inlineStr">
@@ -13797,7 +13797,7 @@
       <c r="K257" s="2" t="inlineStr"/>
       <c r="L257" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13814,12 +13814,12 @@
       </c>
       <c r="C258" s="2" t="inlineStr">
         <is>
-          <t>19:-100--90</t>
+          <t>Ho:19:-100--90</t>
         </is>
       </c>
       <c r="D258" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E258" s="2" t="inlineStr">
@@ -13849,7 +13849,7 @@
       <c r="K258" s="2" t="inlineStr"/>
       <c r="L258" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13866,12 +13866,12 @@
       </c>
       <c r="C259" s="2" t="inlineStr">
         <is>
-          <t>19:-125--100</t>
+          <t>Ho:19:-125--100</t>
         </is>
       </c>
       <c r="D259" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E259" s="2" t="inlineStr">
@@ -13901,7 +13901,7 @@
       <c r="K259" s="2" t="inlineStr"/>
       <c r="L259" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13918,12 +13918,12 @@
       </c>
       <c r="C260" s="2" t="inlineStr">
         <is>
-          <t>19:-150--125</t>
+          <t>Ho:19:-150--125</t>
         </is>
       </c>
       <c r="D260" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E260" s="2" t="inlineStr">
@@ -13953,7 +13953,7 @@
       <c r="K260" s="2" t="inlineStr"/>
       <c r="L260" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -13970,12 +13970,12 @@
       </c>
       <c r="C261" s="2" t="inlineStr">
         <is>
-          <t>19:-175--150</t>
+          <t>Ho:19:-175--150</t>
         </is>
       </c>
       <c r="D261" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E261" s="2" t="inlineStr">
@@ -14005,7 +14005,7 @@
       <c r="K261" s="2" t="inlineStr"/>
       <c r="L261" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14022,12 +14022,12 @@
       </c>
       <c r="C262" s="2" t="inlineStr">
         <is>
-          <t>19:-200--175</t>
+          <t>Ho:19:-200--175</t>
         </is>
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
@@ -14057,7 +14057,7 @@
       <c r="K262" s="2" t="inlineStr"/>
       <c r="L262" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14074,12 +14074,12 @@
       </c>
       <c r="C263" s="2" t="inlineStr">
         <is>
-          <t>19:-216--200</t>
+          <t>Ho:19:-216--200</t>
         </is>
       </c>
       <c r="D263" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E263" s="2" t="inlineStr">
@@ -14109,7 +14109,7 @@
       <c r="K263" s="2" t="inlineStr"/>
       <c r="L263" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14126,12 +14126,12 @@
       </c>
       <c r="C264" s="2" t="inlineStr">
         <is>
-          <t>19:-250--216</t>
+          <t>Ho:19:-250--216</t>
         </is>
       </c>
       <c r="D264" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E264" s="2" t="inlineStr">
@@ -14161,7 +14161,7 @@
       <c r="K264" s="2" t="inlineStr"/>
       <c r="L264" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14178,12 +14178,12 @@
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>20:10-19</t>
+          <t>Hu:20:10-19</t>
         </is>
       </c>
       <c r="D265" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E265" s="2" t="inlineStr">
@@ -14213,7 +14213,7 @@
       <c r="K265" s="2" t="inlineStr"/>
       <c r="L265" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14230,12 +14230,12 @@
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>20:0-10</t>
+          <t>Hu:20:0-10</t>
         </is>
       </c>
       <c r="D266" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E266" s="2" t="inlineStr">
@@ -14265,7 +14265,7 @@
       <c r="K266" s="2" t="inlineStr"/>
       <c r="L266" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14282,12 +14282,12 @@
       </c>
       <c r="C267" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Hu:20:-10-0</t>
         </is>
       </c>
       <c r="D267" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E267" s="2" t="inlineStr">
@@ -14317,7 +14317,7 @@
       <c r="K267" s="2" t="inlineStr"/>
       <c r="L267" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14334,12 +14334,12 @@
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>20:-10-0</t>
+          <t>Ho:20:-10-0</t>
         </is>
       </c>
       <c r="D268" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E268" s="2" t="inlineStr">
@@ -14369,7 +14369,7 @@
       <c r="K268" s="2" t="inlineStr"/>
       <c r="L268" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14386,12 +14386,12 @@
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>20:-20--10</t>
+          <t>Ho:20:-20--10</t>
         </is>
       </c>
       <c r="D269" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E269" s="2" t="inlineStr">
@@ -14421,7 +14421,7 @@
       <c r="K269" s="2" t="inlineStr"/>
       <c r="L269" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14438,12 +14438,12 @@
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>20:-30--20</t>
+          <t>Ho:20:-30--20</t>
         </is>
       </c>
       <c r="D270" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E270" s="2" t="inlineStr">
@@ -14473,7 +14473,7 @@
       <c r="K270" s="2" t="inlineStr"/>
       <c r="L270" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14490,12 +14490,12 @@
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>20:-40--30</t>
+          <t>Ho:20:-40--30</t>
         </is>
       </c>
       <c r="D271" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E271" s="2" t="inlineStr">
@@ -14525,7 +14525,7 @@
       <c r="K271" s="2" t="inlineStr"/>
       <c r="L271" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14542,12 +14542,12 @@
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>20:-50--40</t>
+          <t>Ho:20:-50--40</t>
         </is>
       </c>
       <c r="D272" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E272" s="2" t="inlineStr">
@@ -14577,7 +14577,7 @@
       <c r="K272" s="2" t="inlineStr"/>
       <c r="L272" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14594,12 +14594,12 @@
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>20:-60--50</t>
+          <t>Ho:20:-60--50</t>
         </is>
       </c>
       <c r="D273" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E273" s="2" t="inlineStr">
@@ -14629,7 +14629,7 @@
       <c r="K273" s="2" t="inlineStr"/>
       <c r="L273" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14646,12 +14646,12 @@
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>20:-70--60</t>
+          <t>Ho:20:-70--60</t>
         </is>
       </c>
       <c r="D274" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E274" s="2" t="inlineStr">
@@ -14681,7 +14681,7 @@
       <c r="K274" s="2" t="inlineStr"/>
       <c r="L274" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14698,12 +14698,12 @@
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>20:-80--70</t>
+          <t>Ho:20:-80--70</t>
         </is>
       </c>
       <c r="D275" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E275" s="2" t="inlineStr">
@@ -14733,7 +14733,7 @@
       <c r="K275" s="2" t="inlineStr"/>
       <c r="L275" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>20:-90--80</t>
+          <t>Ho:20:-90--80</t>
         </is>
       </c>
       <c r="D276" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E276" s="2" t="inlineStr">
@@ -14785,7 +14785,7 @@
       <c r="K276" s="2" t="inlineStr"/>
       <c r="L276" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14802,12 +14802,12 @@
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>20:-100--90</t>
+          <t>Ho:20:-100--90</t>
         </is>
       </c>
       <c r="D277" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E277" s="2" t="inlineStr">
@@ -14837,7 +14837,7 @@
       <c r="K277" s="2" t="inlineStr"/>
       <c r="L277" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14854,12 +14854,12 @@
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>20:-125--100</t>
+          <t>Ho:20:-125--100</t>
         </is>
       </c>
       <c r="D278" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E278" s="2" t="inlineStr">
@@ -14889,7 +14889,7 @@
       <c r="K278" s="2" t="inlineStr"/>
       <c r="L278" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14906,12 +14906,12 @@
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>20:-150--125</t>
+          <t>Ho:20:-150--125</t>
         </is>
       </c>
       <c r="D279" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E279" s="2" t="inlineStr">
@@ -14941,7 +14941,7 @@
       <c r="K279" s="2" t="inlineStr"/>
       <c r="L279" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -14958,12 +14958,12 @@
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>20:-175--150</t>
+          <t>Ho:20:-175--150</t>
         </is>
       </c>
       <c r="D280" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E280" s="2" t="inlineStr">
@@ -14993,7 +14993,7 @@
       <c r="K280" s="2" t="inlineStr"/>
       <c r="L280" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15010,12 +15010,12 @@
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>20:-200--175</t>
+          <t>Ho:20:-200--175</t>
         </is>
       </c>
       <c r="D281" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E281" s="2" t="inlineStr">
@@ -15045,7 +15045,7 @@
       <c r="K281" s="2" t="inlineStr"/>
       <c r="L281" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15062,12 +15062,12 @@
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>20:-250--200</t>
+          <t>Ho:20:-250--200</t>
         </is>
       </c>
       <c r="D282" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E282" s="2" t="inlineStr">
@@ -15097,7 +15097,7 @@
       <c r="K282" s="2" t="inlineStr"/>
       <c r="L282" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15114,12 +15114,12 @@
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>20:-300--250</t>
+          <t>Ho:20:-300--250</t>
         </is>
       </c>
       <c r="D283" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E283" s="2" t="inlineStr">
@@ -15149,7 +15149,7 @@
       <c r="K283" s="2" t="inlineStr"/>
       <c r="L283" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15166,12 +15166,12 @@
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>21:10-20</t>
+          <t>Hu:21:10-20</t>
         </is>
       </c>
       <c r="D284" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E284" s="2" t="inlineStr">
@@ -15201,7 +15201,7 @@
       <c r="K284" s="2" t="inlineStr"/>
       <c r="L284" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15218,12 +15218,12 @@
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>21:0-10</t>
+          <t>Hu:21:0-10</t>
         </is>
       </c>
       <c r="D285" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E285" s="2" t="inlineStr">
@@ -15253,7 +15253,7 @@
       <c r="K285" s="2" t="inlineStr"/>
       <c r="L285" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15270,12 +15270,12 @@
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>21:-10-0</t>
+          <t>Ho:21:-10-0</t>
         </is>
       </c>
       <c r="D286" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E286" s="2" t="inlineStr">
@@ -15305,7 +15305,7 @@
       <c r="K286" s="2" t="inlineStr"/>
       <c r="L286" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15322,12 +15322,12 @@
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>21:-20--10</t>
+          <t>Ho:21:-20--10</t>
         </is>
       </c>
       <c r="D287" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E287" s="2" t="inlineStr">
@@ -15357,7 +15357,7 @@
       <c r="K287" s="2" t="inlineStr"/>
       <c r="L287" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15374,12 +15374,12 @@
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>21:-30--20</t>
+          <t>Ho:21:-30--20</t>
         </is>
       </c>
       <c r="D288" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E288" s="2" t="inlineStr">
@@ -15409,7 +15409,7 @@
       <c r="K288" s="2" t="inlineStr"/>
       <c r="L288" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15426,12 +15426,12 @@
       </c>
       <c r="C289" s="2" t="inlineStr">
         <is>
-          <t>21:-40--30</t>
+          <t>Ho:21:-40--30</t>
         </is>
       </c>
       <c r="D289" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E289" s="2" t="inlineStr">
@@ -15461,7 +15461,7 @@
       <c r="K289" s="2" t="inlineStr"/>
       <c r="L289" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15478,12 +15478,12 @@
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>21:-50--40</t>
+          <t>Ho:21:-50--40</t>
         </is>
       </c>
       <c r="D290" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E290" s="2" t="inlineStr">
@@ -15513,7 +15513,7 @@
       <c r="K290" s="2" t="inlineStr"/>
       <c r="L290" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15530,12 +15530,12 @@
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>21:-60--50</t>
+          <t>Ho:21:-60--50</t>
         </is>
       </c>
       <c r="D291" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E291" s="2" t="inlineStr">
@@ -15565,7 +15565,7 @@
       <c r="K291" s="2" t="inlineStr"/>
       <c r="L291" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15582,12 +15582,12 @@
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>21:-70--60</t>
+          <t>Ho:21:-70--60</t>
         </is>
       </c>
       <c r="D292" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E292" s="2" t="inlineStr">
@@ -15617,7 +15617,7 @@
       <c r="K292" s="2" t="inlineStr"/>
       <c r="L292" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15634,12 +15634,12 @@
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>21:-80--70</t>
+          <t>Ho:21:-80--70</t>
         </is>
       </c>
       <c r="D293" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E293" s="2" t="inlineStr">
@@ -15669,7 +15669,7 @@
       <c r="K293" s="2" t="inlineStr"/>
       <c r="L293" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15686,12 +15686,12 @@
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>21:-90--80</t>
+          <t>Ho:21:-90--80</t>
         </is>
       </c>
       <c r="D294" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E294" s="2" t="inlineStr">
@@ -15721,7 +15721,7 @@
       <c r="K294" s="2" t="inlineStr"/>
       <c r="L294" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15738,12 +15738,12 @@
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>21:-100--90</t>
+          <t>Ho:21:-100--90</t>
         </is>
       </c>
       <c r="D295" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E295" s="2" t="inlineStr">
@@ -15773,7 +15773,7 @@
       <c r="K295" s="2" t="inlineStr"/>
       <c r="L295" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15790,12 +15790,12 @@
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>21:-125--100</t>
+          <t>Ho:21:-125--100</t>
         </is>
       </c>
       <c r="D296" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E296" s="2" t="inlineStr">
@@ -15825,7 +15825,7 @@
       <c r="K296" s="2" t="inlineStr"/>
       <c r="L296" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15842,12 +15842,12 @@
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>21:-150--125</t>
+          <t>Ho:21:-150--125</t>
         </is>
       </c>
       <c r="D297" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E297" s="2" t="inlineStr">
@@ -15877,7 +15877,7 @@
       <c r="K297" s="2" t="inlineStr"/>
       <c r="L297" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15894,12 +15894,12 @@
       </c>
       <c r="C298" s="2" t="inlineStr">
         <is>
-          <t>21:-175--150</t>
+          <t>Ho:21:-175--150</t>
         </is>
       </c>
       <c r="D298" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E298" s="2" t="inlineStr">
@@ -15929,7 +15929,7 @@
       <c r="K298" s="2" t="inlineStr"/>
       <c r="L298" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15946,12 +15946,12 @@
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>21:-200--175</t>
+          <t>Ho:21:-200--175</t>
         </is>
       </c>
       <c r="D299" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E299" s="2" t="inlineStr">
@@ -15981,7 +15981,7 @@
       <c r="K299" s="2" t="inlineStr"/>
       <c r="L299" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
@@ -15998,12 +15998,12 @@
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>21:-250--200</t>
+          <t>Ho:21:-250--200</t>
         </is>
       </c>
       <c r="D300" s="2" t="inlineStr">
         <is>
-          <t>Plot:depth</t>
+          <t>Topography:Plot:depth</t>
         </is>
       </c>
       <c r="E300" s="2" t="inlineStr">
@@ -16033,7 +16033,7 @@
       <c r="K300" s="2" t="inlineStr"/>
       <c r="L300" s="2" t="inlineStr">
         <is>
-          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 18 rows share an id</t>
+          <t>lat/long source: doi:10.3334/CDIAC/SPRUCE.005 package spatialCoverage point; source column Zn (ug/g, unit from units row); depth from Top_core_depth, Bottom_core_depth; id not unique: 6 rows share an id</t>
         </is>
       </c>
     </row>
